--- a/artfynd/A 34578-2022 artfynd.xlsx
+++ b/artfynd/A 34578-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118841824</v>
+        <v>118839997</v>
       </c>
       <c r="B2" t="n">
-        <v>56744</v>
+        <v>57771</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102954</v>
+        <v>103018</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,6 +713,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -724,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519647</v>
+        <v>519722</v>
       </c>
       <c r="R2" t="n">
-        <v>6580558</v>
+        <v>6580541</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -754,22 +759,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>06:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>06:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ola Erlandsson</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -800,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118839997</v>
+        <v>118841824</v>
       </c>
       <c r="B3" t="n">
-        <v>57771</v>
+        <v>56744</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,25 +817,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103018</v>
+        <v>102954</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -838,11 +843,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519722</v>
+        <v>519647</v>
       </c>
       <c r="R3" t="n">
-        <v>6580541</v>
+        <v>6580558</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -884,22 +884,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:43</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:43</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,7 +919,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Ola Erlandsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 34578-2022 artfynd.xlsx
+++ b/artfynd/A 34578-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118839997</v>
+        <v>118841824</v>
       </c>
       <c r="B2" t="n">
-        <v>57771</v>
+        <v>56744</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103018</v>
+        <v>102954</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,11 +713,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519722</v>
+        <v>519647</v>
       </c>
       <c r="R2" t="n">
-        <v>6580541</v>
+        <v>6580558</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -759,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>06:43</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>06:43</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Ola Erlandsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -805,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118841824</v>
+        <v>118839997</v>
       </c>
       <c r="B3" t="n">
-        <v>56744</v>
+        <v>57771</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,25 +812,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102954</v>
+        <v>103018</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -843,6 +838,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519647</v>
+        <v>519722</v>
       </c>
       <c r="R3" t="n">
-        <v>6580558</v>
+        <v>6580541</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -884,22 +884,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>06:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>06:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,7 +919,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ola Erlandsson</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
